--- a/upload/estrutura_governamental.xlsx
+++ b/upload/estrutura_governamental.xlsx
@@ -872,9 +872,6 @@
     <t>http://www.meioambiente.mg.gov.br</t>
   </si>
   <si>
-    <t>Marília Carvalho de Melo</t>
-  </si>
-  <si>
     <t>2º andar do Edifício Minas - Cidade Administrativa, Belo Horizonte</t>
   </si>
   <si>
@@ -1047,9 +1044,6 @@
     <t>Kelly Nogueira Guerra</t>
   </si>
   <si>
-    <t>Gleison Cunha Soares</t>
-  </si>
-  <si>
     <t>Paulo Roberto Meireles do Nascimento</t>
   </si>
   <si>
@@ -1605,9 +1599,6 @@
     <t>Coronel Cleide Barcelos dos Reis Rodrigues</t>
   </si>
   <si>
-    <t>Alexandre Ramos Peixoto</t>
-  </si>
-  <si>
     <t>Gustavo de Marchi e Silva</t>
   </si>
   <si>
@@ -1633,13 +1624,22 @@
   </si>
   <si>
     <t>https://www.secult.mg.gov.br/</t>
+  </si>
+  <si>
+    <t>Marco Aurélio Martins da Costa Vasconcelos</t>
+  </si>
+  <si>
+    <t>Augusto Dantas Borges</t>
+  </si>
+  <si>
+    <t>Gilmar Álvares Cota Júnior</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1662,13 +1662,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1702,7 +1695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1711,7 +1704,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -2090,10 +2082,10 @@
         <v>193</v>
       </c>
       <c r="I1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="J1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="K1" t="s">
         <v>128</v>
@@ -2104,7 +2096,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
@@ -2116,7 +2108,7 @@
         <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F2" t="s">
         <v>274</v>
@@ -2125,13 +2117,13 @@
         <v>275</v>
       </c>
       <c r="H2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>173</v>
@@ -2154,28 +2146,28 @@
         <v>9</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G3" t="s">
         <v>208</v>
       </c>
       <c r="H3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>161</v>
       </c>
       <c r="L3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="42.75">
@@ -2201,13 +2193,13 @@
         <v>231</v>
       </c>
       <c r="H4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>186</v>
@@ -2221,7 +2213,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -2239,13 +2231,13 @@
         <v>228</v>
       </c>
       <c r="H5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>158</v>
@@ -2256,10 +2248,10 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -2268,28 +2260,28 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
+        <v>475</v>
+      </c>
+      <c r="F6" t="s">
+        <v>478</v>
+      </c>
+      <c r="G6" t="s">
+        <v>285</v>
+      </c>
+      <c r="H6" t="s">
+        <v>476</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="F6" t="s">
-        <v>480</v>
-      </c>
-      <c r="G6" t="s">
-        <v>286</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
+        <v>356</v>
+      </c>
+      <c r="K6" t="s">
+        <v>503</v>
+      </c>
+      <c r="L6" t="s">
         <v>478</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="J6" t="s">
-        <v>358</v>
-      </c>
-      <c r="K6" t="s">
-        <v>505</v>
-      </c>
-      <c r="L6" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2306,28 +2298,28 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G7" t="s">
         <v>232</v>
       </c>
       <c r="H7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="I7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>190</v>
       </c>
       <c r="L7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2344,28 +2336,28 @@
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G8" t="s">
         <v>225</v>
       </c>
       <c r="H8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>170</v>
       </c>
       <c r="L8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2382,7 +2374,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="F9" t="s">
         <v>241</v>
@@ -2391,13 +2383,13 @@
         <v>243</v>
       </c>
       <c r="H9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>188</v>
@@ -2408,7 +2400,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B10" t="s">
         <v>79</v>
@@ -2420,28 +2412,28 @@
         <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G10" t="s">
         <v>273</v>
       </c>
       <c r="H10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="I10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>172</v>
       </c>
       <c r="L10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2458,7 +2450,7 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F11" t="s">
         <v>242</v>
@@ -2467,13 +2459,13 @@
         <v>249</v>
       </c>
       <c r="H11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J11" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>189</v>
@@ -2496,7 +2488,7 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F12" t="s">
         <v>247</v>
@@ -2505,13 +2497,13 @@
         <v>248</v>
       </c>
       <c r="H12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="I12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J12" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>187</v>
@@ -2534,7 +2526,7 @@
         <v>34</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>281</v>
+        <v>533</v>
       </c>
       <c r="F13" t="s">
         <v>240</v>
@@ -2543,13 +2535,13 @@
         <v>246</v>
       </c>
       <c r="H13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>153</v>
@@ -2572,7 +2564,7 @@
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F14" t="s">
         <v>219</v>
@@ -2581,13 +2573,13 @@
         <v>225</v>
       </c>
       <c r="H14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="I14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J14" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>162</v>
@@ -2598,10 +2590,10 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -2610,28 +2602,28 @@
         <v>26</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G15" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H15">
         <v>155</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J15" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K15" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="L15" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2648,31 +2640,31 @@
         <v>23</v>
       </c>
       <c r="E16" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G16" t="s">
         <v>239</v>
       </c>
       <c r="H16" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="I16" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J16" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>142</v>
       </c>
       <c r="L16" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -2685,8 +2677,8 @@
       <c r="D17" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>533</v>
+      <c r="E17" t="s">
+        <v>530</v>
       </c>
       <c r="F17" t="s">
         <v>236</v>
@@ -2695,13 +2687,13 @@
         <v>237</v>
       </c>
       <c r="H17" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I17" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J17" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>137</v>
@@ -2724,28 +2716,28 @@
         <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G18" t="s">
         <v>238</v>
       </c>
       <c r="H18" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>141</v>
       </c>
       <c r="L18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -2765,25 +2757,25 @@
         <v>271</v>
       </c>
       <c r="F19" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G19" t="s">
         <v>272</v>
       </c>
       <c r="H19" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="I19" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J19" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>166</v>
       </c>
       <c r="L19" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -2800,28 +2792,28 @@
         <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G20" t="s">
         <v>263</v>
       </c>
       <c r="H20" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J20" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>135</v>
       </c>
       <c r="L20" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -2838,28 +2830,28 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F21" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G21" t="s">
         <v>264</v>
       </c>
       <c r="H21" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I21" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J21" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>152</v>
       </c>
       <c r="L21" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -2876,33 +2868,33 @@
         <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F22" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G22" t="s">
         <v>265</v>
       </c>
       <c r="H22" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I22" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J22" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>134</v>
       </c>
       <c r="L22" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B23" t="s">
         <v>113</v>
@@ -2914,7 +2906,7 @@
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>259</v>
@@ -2923,13 +2915,13 @@
         <v>207</v>
       </c>
       <c r="H23" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I23" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J23" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>157</v>
@@ -2961,13 +2953,13 @@
         <v>256</v>
       </c>
       <c r="H24" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="I24" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="J24" t="s">
         <v>385</v>
-      </c>
-      <c r="J24" t="s">
-        <v>387</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>145</v>
@@ -2999,13 +2991,13 @@
         <v>254</v>
       </c>
       <c r="H25" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="I25" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J25" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>174</v>
@@ -3028,7 +3020,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F26" t="s">
         <v>222</v>
@@ -3037,13 +3029,13 @@
         <v>252</v>
       </c>
       <c r="H26" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J26" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>154</v>
@@ -3069,25 +3061,25 @@
         <v>260</v>
       </c>
       <c r="F27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G27" t="s">
         <v>248</v>
       </c>
       <c r="H27" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I27" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J27" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>144</v>
       </c>
       <c r="L27" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -3113,13 +3105,13 @@
         <v>258</v>
       </c>
       <c r="H28" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I28" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J28" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>175</v>
@@ -3130,10 +3122,10 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B29" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C29" t="s">
         <v>44</v>
@@ -3142,28 +3134,28 @@
         <v>34</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F29" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G29" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H29">
         <v>117</v>
       </c>
       <c r="I29" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J29" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K29" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="L29" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -3189,13 +3181,13 @@
         <v>270</v>
       </c>
       <c r="H30" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J30" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>169</v>
@@ -3218,7 +3210,7 @@
         <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>224</v>
@@ -3227,13 +3219,13 @@
         <v>250</v>
       </c>
       <c r="H31" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="I31" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J31" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>176</v>
@@ -3258,20 +3250,20 @@
       <c r="E32" t="s">
         <v>217</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="2" t="s">
         <v>216</v>
       </c>
       <c r="G32" t="s">
         <v>218</v>
       </c>
       <c r="H32" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I32" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J32" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>148</v>
@@ -3294,22 +3286,22 @@
         <v>6</v>
       </c>
       <c r="E33" t="s">
-        <v>527</v>
-      </c>
-      <c r="F33" t="s">
+        <v>524</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>212</v>
       </c>
       <c r="G33" t="s">
         <v>207</v>
       </c>
       <c r="H33" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="I33" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J33" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>156</v>
@@ -3320,7 +3312,7 @@
     </row>
     <row r="34" spans="1:12" ht="42.75">
       <c r="A34" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s">
         <v>74</v>
@@ -3332,28 +3324,28 @@
         <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G34" t="s">
         <v>251</v>
       </c>
       <c r="H34" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="I34" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J34" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>133</v>
       </c>
       <c r="L34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -3379,13 +3371,13 @@
         <v>207</v>
       </c>
       <c r="H35" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I35" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J35" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>185</v>
@@ -3411,25 +3403,25 @@
         <v>210</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G36" t="s">
         <v>211</v>
       </c>
       <c r="H36" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I36" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J36" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>140</v>
       </c>
       <c r="L36" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -3446,7 +3438,7 @@
         <v>34</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F37" t="s">
         <v>235</v>
@@ -3455,13 +3447,13 @@
         <v>218</v>
       </c>
       <c r="H37" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="I37" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J37" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>183</v>
@@ -3484,7 +3476,7 @@
         <v>26</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F38" t="s">
         <v>203</v>
@@ -3493,13 +3485,13 @@
         <v>215</v>
       </c>
       <c r="H38" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="I38" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="J38" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>178</v>
@@ -3528,16 +3520,16 @@
         <v>204</v>
       </c>
       <c r="G39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H39" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I39" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J39" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>179</v>
@@ -3560,22 +3552,22 @@
         <v>31</v>
       </c>
       <c r="E40" t="s">
-        <v>341</v>
-      </c>
-      <c r="F40" t="s">
+        <v>339</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>205</v>
       </c>
       <c r="G40" t="s">
         <v>213</v>
       </c>
       <c r="H40" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I40" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J40" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K40" t="s">
         <v>184</v>
@@ -3598,7 +3590,7 @@
         <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>200</v>
@@ -3607,13 +3599,13 @@
         <v>201</v>
       </c>
       <c r="H41" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="I41" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J41" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>151</v>
@@ -3636,7 +3628,7 @@
         <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>199</v>
@@ -3645,13 +3637,13 @@
         <v>208</v>
       </c>
       <c r="H42" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="J42" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>150</v>
@@ -3662,10 +3654,10 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C43" t="s">
         <v>44</v>
@@ -3674,28 +3666,28 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
+        <v>286</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="F43" t="s">
-        <v>288</v>
-      </c>
       <c r="G43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H43" t="s">
+        <v>481</v>
+      </c>
+      <c r="I43" t="s">
         <v>483</v>
       </c>
-      <c r="I43" t="s">
-        <v>485</v>
-      </c>
       <c r="J43" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K43" t="s">
         <v>163</v>
       </c>
       <c r="L43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -3712,28 +3704,28 @@
         <v>34</v>
       </c>
       <c r="E44" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F44" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H44" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I44" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J44" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>183</v>
       </c>
       <c r="L44" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -3750,7 +3742,7 @@
         <v>34</v>
       </c>
       <c r="E45" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F45" t="s">
         <v>233</v>
@@ -3759,13 +3751,13 @@
         <v>234</v>
       </c>
       <c r="H45" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J45" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>182</v>
@@ -3788,7 +3780,7 @@
         <v>31</v>
       </c>
       <c r="E46" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>267</v>
@@ -3797,13 +3789,13 @@
         <v>273</v>
       </c>
       <c r="H46" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="I46" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J46" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>171</v>
@@ -3826,28 +3818,28 @@
         <v>31</v>
       </c>
       <c r="E47" t="s">
-        <v>347</v>
-      </c>
-      <c r="F47" t="s">
-        <v>317</v>
+        <v>345</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="G47" t="s">
         <v>266</v>
       </c>
       <c r="H47" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="I47" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J47" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>168</v>
       </c>
       <c r="L47" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -3864,7 +3856,7 @@
         <v>31</v>
       </c>
       <c r="E48" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>191</v>
@@ -3873,13 +3865,13 @@
         <v>213</v>
       </c>
       <c r="H48" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="I48" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J48" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>167</v>
@@ -3902,22 +3894,22 @@
         <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>313</v>
-      </c>
-      <c r="F49" t="s">
+        <v>312</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>244</v>
       </c>
       <c r="G49" t="s">
         <v>245</v>
       </c>
       <c r="H49" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I49" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J49" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>181</v>
@@ -3940,28 +3932,28 @@
         <v>31</v>
       </c>
       <c r="E50" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G50" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H50" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="I50" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J50" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>139</v>
       </c>
       <c r="L50" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3978,28 +3970,28 @@
         <v>31</v>
       </c>
       <c r="E51" t="s">
+        <v>299</v>
+      </c>
+      <c r="F51" t="s">
+        <v>348</v>
+      </c>
+      <c r="G51" t="s">
         <v>300</v>
       </c>
-      <c r="F51" t="s">
-        <v>350</v>
-      </c>
-      <c r="G51" t="s">
-        <v>301</v>
-      </c>
       <c r="H51" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I51" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="J51" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>131</v>
       </c>
       <c r="L51" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -4016,28 +4008,28 @@
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F52" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G52" t="s">
         <v>298</v>
       </c>
-      <c r="G52" t="s">
-        <v>299</v>
-      </c>
       <c r="H52" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I52" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J52" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>138</v>
       </c>
       <c r="L52" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -4054,28 +4046,28 @@
         <v>31</v>
       </c>
       <c r="E53" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="G53" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H53" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I53" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J53" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>136</v>
       </c>
       <c r="L53" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -4092,28 +4084,28 @@
         <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F54" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G54" t="s">
         <v>218</v>
       </c>
       <c r="H54" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I54" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="J54" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>132</v>
       </c>
       <c r="L54" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -4130,28 +4122,28 @@
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F55" t="s">
+        <v>294</v>
+      </c>
+      <c r="G55" t="s">
         <v>295</v>
       </c>
-      <c r="G55" t="s">
-        <v>296</v>
-      </c>
       <c r="H55" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I55" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J55" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>149</v>
       </c>
       <c r="L55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -4168,28 +4160,28 @@
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F56" t="s">
+        <v>292</v>
+      </c>
+      <c r="G56" t="s">
         <v>293</v>
       </c>
-      <c r="G56" t="s">
-        <v>294</v>
-      </c>
       <c r="H56" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J56" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>146</v>
       </c>
       <c r="L56" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -4206,28 +4198,28 @@
         <v>31</v>
       </c>
       <c r="E57" t="s">
-        <v>515</v>
-      </c>
-      <c r="F57" t="s">
+        <v>513</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G57" t="s">
         <v>291</v>
       </c>
-      <c r="G57" t="s">
-        <v>292</v>
-      </c>
       <c r="H57" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I57" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J57" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>165</v>
       </c>
       <c r="L57" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -4244,28 +4236,28 @@
         <v>31</v>
       </c>
       <c r="E58" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F58" t="s">
+        <v>288</v>
+      </c>
+      <c r="G58" t="s">
         <v>289</v>
       </c>
-      <c r="G58" t="s">
-        <v>290</v>
-      </c>
       <c r="H58" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="I58" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J58" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>164</v>
       </c>
       <c r="L58" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -4282,28 +4274,28 @@
         <v>31</v>
       </c>
       <c r="E59" t="s">
+        <v>286</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="F59" t="s">
-        <v>288</v>
-      </c>
       <c r="G59" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H59" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="I59" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J59" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>163</v>
       </c>
       <c r="L59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -4320,28 +4312,28 @@
         <v>31</v>
       </c>
       <c r="E60" t="s">
+        <v>283</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G60" t="s">
         <v>284</v>
       </c>
-      <c r="F60" t="s">
-        <v>283</v>
-      </c>
-      <c r="G60" t="s">
-        <v>285</v>
-      </c>
       <c r="H60" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="I60" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J60" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L60" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -4358,22 +4350,22 @@
         <v>31</v>
       </c>
       <c r="E61" t="s">
-        <v>351</v>
-      </c>
-      <c r="F61" t="s">
+        <v>349</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>280</v>
       </c>
       <c r="G61" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H61" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="I61" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J61" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>159</v>
@@ -4396,22 +4388,22 @@
         <v>31</v>
       </c>
       <c r="E62" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F62" t="s">
         <v>279</v>
       </c>
       <c r="G62" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H62" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="I62" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J62" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>155</v>
@@ -4436,20 +4428,20 @@
       <c r="E63" t="s">
         <v>277</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="2" t="s">
         <v>276</v>
       </c>
       <c r="G63" t="s">
         <v>278</v>
       </c>
       <c r="H63" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="I63" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J63" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>177</v>
@@ -4460,7 +4452,7 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B64" t="s">
         <v>110</v>
@@ -4472,28 +4464,28 @@
         <v>31</v>
       </c>
       <c r="E64" t="s">
+        <v>419</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G64" t="s">
+        <v>298</v>
+      </c>
+      <c r="H64" t="s">
         <v>421</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G64" t="s">
-        <v>299</v>
-      </c>
-      <c r="H64" t="s">
-        <v>423</v>
-      </c>
       <c r="I64" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J64" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>130</v>
       </c>
       <c r="L64" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -4510,7 +4502,7 @@
         <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>198</v>
@@ -4519,13 +4511,13 @@
         <v>209</v>
       </c>
       <c r="H65" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="I65" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J65" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>180</v>
@@ -4557,13 +4549,13 @@
         <v>197</v>
       </c>
       <c r="H66" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="I66" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J66" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K66" t="s">
         <v>143</v>
@@ -4586,7 +4578,7 @@
         <v>16</v>
       </c>
       <c r="E67" t="s">
-        <v>339</v>
+        <v>534</v>
       </c>
       <c r="F67" t="s">
         <v>261</v>
@@ -4595,13 +4587,13 @@
         <v>262</v>
       </c>
       <c r="H67" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="I67" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J67" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>147</v>
@@ -4778,8 +4770,10 @@
     <hyperlink ref="F36" r:id="rId159"/>
     <hyperlink ref="F50" r:id="rId160"/>
     <hyperlink ref="F52" r:id="rId161"/>
+    <hyperlink ref="F43" r:id="rId162"/>
+    <hyperlink ref="F53" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId162"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId164"/>
 </worksheet>
 </file>